--- a/data/trans_camb/IQ26A_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IQ26A_R2-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>23,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,0</t>
+          <t>13,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 2,83</t>
+          <t>-4,79; 7,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,25</t>
+          <t>-3,0; 8,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,02; 39,96</t>
+          <t>-3,59; 20,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 7,55</t>
+          <t>-7,58; 2,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,76</t>
+          <t>1,16; 14,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 21,04</t>
+          <t>11,57; 39,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,19</t>
+          <t>-3,91; 3,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,86</t>
+          <t>1,14; 9,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 22,49</t>
+          <t>4,93; 24,63</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67,59%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-31,26%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>287,73%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>286,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>157,8%</t>
+          <t>166,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 62,68</t>
+          <t>-42,67; 133,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 254,13</t>
+          <t>-28,03; 145,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98,25; 631,32</t>
+          <t>-43,02; 337,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 133,69</t>
+          <t>-70,57; 43,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 148,84</t>
+          <t>3,74; 237,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 345,21</t>
+          <t>104,35; 645,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 45,19</t>
+          <t>-39,35; 52,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 149,66</t>
+          <t>10,83; 147,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,88; 326,66</t>
+          <t>49,21; 369,49</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-6,58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 0,23</t>
+          <t>-8,7; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -1,32</t>
+          <t>-6,85; 3,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 17,03</t>
+          <t>0,04; 20,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 1,49</t>
+          <t>-11,34; 0,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 3,06</t>
+          <t>-12,18; -1,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 18,36</t>
+          <t>-7,72; 15,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,67</t>
+          <t>-8,02; -0,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -0,5</t>
+          <t>-7,69; -0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 14,03</t>
+          <t>-1,4; 14,51</t>
         </is>
       </c>
     </row>
@@ -951,27 +951,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>-13,75%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-29,26%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>-38,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-29,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-13,75%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 2,19</t>
+          <t>-56,73; 13,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,45; -7,75</t>
+          <t>-46,06; 38,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 117,68</t>
+          <t>0,72; 189,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 17,79</t>
+          <t>-53,65; 5,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 30,33</t>
+          <t>-59,21; -10,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 168,58</t>
+          <t>-44,29; 101,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,74; -3,75</t>
+          <t>-47,63; -4,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -3,79</t>
+          <t>-46,56; -2,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 103,74</t>
+          <t>-8,62; 106,72</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,23</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,99</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,74</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>16,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>12,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 6,88</t>
+          <t>-6,55; 4,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,39</t>
+          <t>-2,99; 9,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 27,79</t>
+          <t>-2,11; 23,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,66</t>
+          <t>-4,23; 7,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,73</t>
+          <t>2,57; 15,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 19,29</t>
+          <t>3,17; 32,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,13</t>
+          <t>-3,96; 4,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,75</t>
+          <t>1,52; 11,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 19,75</t>
+          <t>3,71; 22,9</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-7,17%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75,66%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>86,59%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132,44%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-7,17%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,45%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>157,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>107,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 91,42</t>
+          <t>-43,47; 50,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,01; 213,66</t>
+          <t>-21,51; 105,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 348,38</t>
+          <t>-16,17; 227,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,72; 55,36</t>
+          <t>-34,56; 93,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 109,31</t>
+          <t>17,28; 207,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 195,3</t>
+          <t>21,64; 399,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 43,7</t>
+          <t>-29,43; 47,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,18; 127,23</t>
+          <t>10,94; 118,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,95; 208,74</t>
+          <t>24,96; 223,78</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-4,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,06</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,58</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 1,64</t>
+          <t>-5,94; 5,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,95</t>
+          <t>-0,73; 11,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 22,64</t>
+          <t>-7,7; 13,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,31</t>
+          <t>-9,92; 1,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 11,67</t>
+          <t>-7,91; 3,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 17,12</t>
+          <t>-6,51; 15,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,72</t>
+          <t>-6,32; 1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 5,97</t>
+          <t>-2,63; 6,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 15,34</t>
+          <t>-4,24; 11,19</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-1,35%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38,65%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-26,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-12,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>47,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,35%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>38,65%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 13,52</t>
+          <t>-33,82; 48,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 32,45</t>
+          <t>-3,94; 103,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 158,9</t>
+          <t>-49,32; 116,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 44,12</t>
+          <t>-50,85; 14,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 102,86</t>
+          <t>-42,5; 28,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 131,69</t>
+          <t>-37,23; 114,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 12,3</t>
+          <t>-36,87; 13,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 43,36</t>
+          <t>-15,1; 49,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 108,67</t>
+          <t>-27,52; 79,64</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,41</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10,59</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,15</t>
+          <t>-3,91; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,97</t>
+          <t>-0,53; 5,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 18,08</t>
+          <t>1,58; 12,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,92</t>
+          <t>-6,06; -0,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,57</t>
+          <t>-1,95; 4,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 12,5</t>
+          <t>4,06; 17,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,14</t>
+          <t>-3,97; 0,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,86</t>
+          <t>-0,36; 4,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,27</t>
+          <t>3,96; 12,6</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-8,56%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>54,43%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,98%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>77,67%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-8,56%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -0,51</t>
+          <t>-30,23; 15,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 32,64</t>
+          <t>-4,16; 49,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34,29; 142,83</t>
+          <t>11,39; 113,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 19,13</t>
+          <t>-40,28; -0,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 51,08</t>
+          <t>-12,82; 34,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,11; 109,75</t>
+          <t>27,11; 137,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -1,21</t>
+          <t>-28,75; -0,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 33,23</t>
+          <t>-2,56; 33,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29,2; 101,06</t>
+          <t>29,18; 103,04</t>
         </is>
       </c>
     </row>
